--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
@@ -912,66 +912,66 @@
   </si>
   <si>
     <t>214
-163</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>R$ 1.674.923,38</t>
-  </si>
-  <si>
-    <t>R$ 9.681,64
-R$ 9.889,87</t>
-  </si>
-  <si>
-    <t>12.1%
-14.5%</t>
-  </si>
-  <si>
-    <t>101.9</t>
+166</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>R$ 1.705.397,12</t>
+  </si>
+  <si>
+    <t>R$ 9.689,76
+R$ 9.894,71</t>
+  </si>
+  <si>
+    <t>12.2%
+14.6%</t>
+  </si>
+  <si>
+    <t>102.0</t>
   </si>
   <si>
     <t>6.4%</t>
   </si>
   <si>
-    <t>35.5%</t>
-  </si>
-  <si>
-    <t>(11.5%)</t>
-  </si>
-  <si>
-    <t>2.6%</t>
+    <t>45.3%</t>
+  </si>
+  <si>
+    <t>(1.3%)</t>
+  </si>
+  <si>
+    <t>2.5%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>31.2</t>
-  </si>
-  <si>
-    <t>54.3%</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>8.7</t>
-  </si>
-  <si>
-    <t>15.6</t>
-  </si>
-  <si>
-    <t>22.4</t>
-  </si>
-  <si>
-    <t>56.6%</t>
-  </si>
-  <si>
-    <t>-R$ 38.037,14</t>
+    <t>31.3</t>
+  </si>
+  <si>
+    <t>54.0%</t>
+  </si>
+  <si>
+    <t>20.7%</t>
+  </si>
+  <si>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>56.3%</t>
+  </si>
+  <si>
+    <t>-R$ 37.772,94</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2947,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2983,25 +2983,59 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
+      <c r="O13" s="5">
+        <v>15512</v>
+      </c>
+      <c r="P13" s="5">
+        <v>15512</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0.10039001703930395</v>
+      </c>
+      <c r="R13" s="7">
+        <v>162</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0.072847682119205226</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.41555143759669938</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.06542508380608561</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.020899355337802992</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.015176689014956163</v>
+      </c>
+      <c r="X13" s="8">
+        <v>37.612307692307695</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.48461538461538461</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>14.067272727272726</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>7.4516669230769228</v>
+      </c>
       <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="AD13" s="8">
+        <v>29.772307692307692</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.36153846153846153</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>264.19999999999999</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -3120,7 +3154,9 @@
       <c r="AB14" s="8">
         <v>6.1651993710691828</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>19.696135999999999</v>
+      </c>
       <c r="AD14" s="8">
         <v>26.538333125000001</v>
       </c>
@@ -5011,7 +5047,9 @@
       <c r="AB29" s="8">
         <v>24.227017894736839</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>32.750067000000001</v>
+      </c>
       <c r="AD29" s="8">
         <v>40.88894736842105</v>
       </c>
@@ -6247,7 +6285,9 @@
       <c r="AB39" s="8">
         <v>6.280951948051948</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>8.9107430000000001</v>
+      </c>
       <c r="AD39" s="8">
         <v>16.6299582278481</v>
       </c>
@@ -6733,7 +6773,9 @@
       <c r="AB43" s="8">
         <v>13.504166666666666</v>
       </c>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="8">
+        <v>19.439813999999998</v>
+      </c>
       <c r="AD43" s="8">
         <v>26.375</v>
       </c>
@@ -6862,7 +6904,9 @@
       <c r="AB44" s="8">
         <v>4.0986666666666665</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>7.2102880000000003</v>
+      </c>
       <c r="AD44" s="8">
         <v>15.069078947368421</v>
       </c>
@@ -7638,7 +7682,9 @@
       <c r="AB50" s="8">
         <v>9.630054918032787</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>12.544301000000001</v>
+      </c>
       <c r="AD50" s="8">
         <v>20.247580645161289</v>
       </c>
@@ -8122,7 +8168,9 @@
       <c r="AB54" s="8">
         <v>15.558333333333334</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>22.809401000000001</v>
+      </c>
       <c r="AD54" s="8">
         <v>29.717948717948719</v>
       </c>
@@ -8251,7 +8299,9 @@
       <c r="AB55" s="8">
         <v>15.997154878048779</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>19.596122999999999</v>
+      </c>
       <c r="AD55" s="8">
         <v>26.137103571428572</v>
       </c>
@@ -8378,7 +8428,9 @@
       <c r="AB56" s="8">
         <v>4.1284482758620689</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>11.630209000000001</v>
+      </c>
       <c r="AD56" s="8">
         <v>19.683471074380165</v>
       </c>
@@ -10217,7 +10269,9 @@
       <c r="AB71" s="8">
         <v>4.8113636363636365</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>9.2397310000000008</v>
+      </c>
       <c r="AD71" s="8">
         <v>16.747517021276597</v>
       </c>
@@ -10344,7 +10398,9 @@
       <c r="AB72" s="8">
         <v>6.9914730232558142</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>15.855613999999999</v>
+      </c>
       <c r="AD72" s="8">
         <v>22.703023255813953</v>
       </c>
@@ -10693,7 +10749,9 @@
       <c r="AB75" s="8">
         <v>5.1794433333333334</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>11.922454</v>
+      </c>
       <c r="AD75" s="8">
         <v>18.532258064516128</v>
       </c>
@@ -12454,7 +12512,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12490,25 +12548,61 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
-      <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="O90" s="5">
+        <v>8103.5299999999997</v>
+      </c>
+      <c r="P90" s="5">
+        <v>8103.5299999999997</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.41907278598496789</v>
+      </c>
+      <c r="R90" s="7">
+        <v>79</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.067567567567567544</v>
+      </c>
+      <c r="T90" s="6">
+        <v>20.385527677444273</v>
+      </c>
+      <c r="U90" s="6">
+        <v>20.385527677444273</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.015921888362232264</v>
+      </c>
+      <c r="W90" s="6">
+        <v>-0.010449335042876377</v>
+      </c>
+      <c r="X90" s="8">
+        <v>45.54032258064516</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.72580645161290325</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>14.025406097560976</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>21.194624193548389</v>
+      </c>
+      <c r="AC90" s="8">
+        <v>35.745905</v>
+      </c>
+      <c r="AD90" s="8">
+        <v>42.885483870967747</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.17741935483870969</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>0</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -13607,10 +13701,10 @@
         <v>0.21739130434782616</v>
       </c>
       <c r="T99" s="6">
-        <v>-0.13973380421414941</v>
+        <v>0.24403547068266673</v>
       </c>
       <c r="U99" s="6">
-        <v>-0.39669907870297283</v>
+        <v>-0.012929803806156662</v>
       </c>
       <c r="V99" s="6">
         <v>0.01250679717237629</v>
@@ -13633,7 +13727,9 @@
       <c r="AB99" s="8">
         <v>16.496407758620691</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>26.244147999999999</v>
+      </c>
       <c r="AD99" s="8">
         <v>32.841525423728818</v>
       </c>
@@ -13944,7 +14040,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -13980,25 +14076,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>6858.21</v>
+      </c>
+      <c r="P102" s="5">
+        <v>6858.21</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.20228564015630268</v>
+      </c>
+      <c r="R102" s="7">
+        <v>77</v>
+      </c>
+      <c r="S102" s="6">
+        <v>0.11594202898550732</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.34199885976078304</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.018062439032925502</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.0013277517019747134</v>
+      </c>
+      <c r="X102" s="8">
+        <v>26.413332727272728</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.12727272727272726</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>6.7989716049382709</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>6.9260416666666664</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>18.919090909090908</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.69090909090909092</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -14508,7 +14638,9 @@
       <c r="AB106" s="8">
         <v>1.4345536585365852</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>5.9670909999999999</v>
+      </c>
       <c r="AD106" s="8">
         <v>12.939024390243903</v>
       </c>
@@ -14859,7 +14991,9 @@
       <c r="AB109" s="8">
         <v>29.549478125</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>35.693229000000002</v>
+      </c>
       <c r="AD109" s="8">
         <v>43.622396875</v>
       </c>
@@ -15081,7 +15215,9 @@
       <c r="AB111" s="8">
         <v>1.075</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>4.9694440000000002</v>
+      </c>
       <c r="AD111" s="8">
         <v>11.944450000000002</v>
       </c>
@@ -16700,7 +16836,9 @@
       <c r="AB124" s="8">
         <v>26.589583333333334</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>32.246527</v>
+      </c>
       <c r="AD124" s="8">
         <v>40.205554166666666</v>
       </c>
@@ -19333,7 +19471,9 @@
       <c r="AB145" s="8">
         <v>3.8007085106382976</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>11.929411999999999</v>
+      </c>
       <c r="AD145" s="8">
         <v>16.396990277777778</v>
       </c>
@@ -19857,7 +19997,9 @@
       <c r="AB149" s="8">
         <v>5.8583499999999997</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>11.887499</v>
+      </c>
       <c r="AD149" s="8">
         <v>17.449999999999999</v>
       </c>
@@ -21184,7 +21326,9 @@
       <c r="AB160" s="8">
         <v>19.365476190476191</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>26.191057000000001</v>
+      </c>
       <c r="AD160" s="8">
         <v>33.107539285714289</v>
       </c>
@@ -22797,7 +22941,9 @@
       <c r="AB173" s="8">
         <v>14.81875</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>23.422083000000001</v>
+      </c>
       <c r="AD173" s="8">
         <v>20.403030303030302</v>
       </c>
@@ -23057,7 +23203,9 @@
       <c r="AB175" s="8">
         <v>2.5429499999999998</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>14.191798</v>
+      </c>
       <c r="AD175" s="8">
         <v>20.610344827586207</v>
       </c>
@@ -23831,7 +23979,9 @@
       <c r="AB181" s="8">
         <v>0.86754210526315789</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>6.2962949999999998</v>
+      </c>
       <c r="AD181" s="8">
         <v>13.064368965517241</v>
       </c>
@@ -24577,7 +24727,9 @@
       <c r="AB187" s="8">
         <v>9.8300000000000001</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>14.992222</v>
+      </c>
       <c r="AD187" s="8">
         <v>21.956666666666667</v>
       </c>
@@ -24839,7 +24991,9 @@
       <c r="AB189" s="8">
         <v>13.476785714285715</v>
       </c>
-      <c r="AC189" s="8"/>
+      <c r="AC189" s="8">
+        <v>17.877934</v>
+      </c>
       <c r="AD189" s="8">
         <v>24.180746551724141</v>
       </c>
@@ -25750,7 +25904,9 @@
       <c r="AB196" s="8">
         <v>20.353335000000001</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>35.662855999999998</v>
+      </c>
       <c r="AD196" s="8">
         <v>41.326190476190476</v>
       </c>
@@ -26272,7 +26428,9 @@
       <c r="AB200" s="8">
         <v>3.5166666666666666</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>11.884999000000001</v>
+      </c>
       <c r="AD200" s="8">
         <v>17.25</v>
       </c>
@@ -26845,7 +27003,9 @@
       <c r="AB205" s="8">
         <v>7.1324578947368416</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>11.479281</v>
+      </c>
       <c r="AD205" s="8">
         <v>17.492857142857144</v>
       </c>
@@ -26970,7 +27130,9 @@
       <c r="AB206" s="8">
         <v>6.9758349999999991</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>15.02962</v>
+      </c>
       <c r="AD206" s="8">
         <v>21.941271428571429</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
@@ -912,48 +912,48 @@
   </si>
   <si>
     <t>214
-166</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>R$ 1.705.397,12</t>
-  </si>
-  <si>
-    <t>R$ 9.689,76
-R$ 9.894,71</t>
-  </si>
-  <si>
-    <t>12.2%
-14.6%</t>
-  </si>
-  <si>
-    <t>102.0</t>
-  </si>
-  <si>
-    <t>6.4%</t>
-  </si>
-  <si>
-    <t>45.3%</t>
-  </si>
-  <si>
-    <t>(1.3%)</t>
-  </si>
-  <si>
-    <t>2.5%</t>
+170</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 1.757.527,31</t>
+  </si>
+  <si>
+    <t>R$ 9.764,04
+R$ 9.968,54</t>
+  </si>
+  <si>
+    <t>12.5%
+14.7%</t>
+  </si>
+  <si>
+    <t>102.6</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>44.6%</t>
+  </si>
+  <si>
+    <t>(1.6%)</t>
+  </si>
+  <si>
+    <t>2.6%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>31.3</t>
-  </si>
-  <si>
-    <t>54.0%</t>
-  </si>
-  <si>
-    <t>20.7%</t>
+    <t>31.5</t>
+  </si>
+  <si>
+    <t>53.9%</t>
+  </si>
+  <si>
+    <t>21.0%</t>
   </si>
   <si>
     <t>6.9</t>
@@ -962,16 +962,16 @@
     <t>8.8</t>
   </si>
   <si>
-    <t>16.0</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>56.3%</t>
-  </si>
-  <si>
-    <t>-R$ 37.772,94</t>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>22.7</t>
+  </si>
+  <si>
+    <t>55.8%</t>
+  </si>
+  <si>
+    <t>-R$ 39.957,06</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1411,7 +1411,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>19283.93</v>
+      </c>
+      <c r="P6" s="5">
+        <v>19283.93</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.65651428065838169</v>
+      </c>
+      <c r="R6" s="7">
+        <v>171</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.29545454545454541</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.29020218907660417</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0080912604432810103</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.021113974174351388</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.00077061055500616312</v>
+      </c>
+      <c r="X6" s="8">
+        <v>29.363199328859057</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.70469798657718119</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.12751677852348994</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>12.456395348837209</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.1299547297297297</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>15.960953999999999</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>22.911968456375838</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.51006711409395977</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -3025,7 +3061,9 @@
       <c r="AB13" s="8">
         <v>7.4516669230769228</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>22.832435</v>
+      </c>
       <c r="AD13" s="8">
         <v>29.772307692307692</v>
       </c>
@@ -4874,7 +4912,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4910,25 +4948,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>12907.67</v>
+      </c>
+      <c r="P28" s="5">
+        <v>12907.67</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.3176120274472094</v>
+      </c>
+      <c r="R28" s="7">
+        <v>121</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.11009174311926606</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00023599146863841422</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.31934221280835345</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.029713495929164595</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.023679874059377097</v>
+      </c>
+      <c r="X28" s="8">
+        <v>31.600249253731342</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.48529411764705882</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.17910447761194029</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>4.1789256198347102</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>11.017910447761194</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>15.276367</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>22.190049253731345</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.5074626865671642</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-1987.8199999999999</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -9174,7 +9248,9 @@
       <c r="AB62" s="8">
         <v>7.0955134615384612</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8">
+        <v>10.166724</v>
+      </c>
       <c r="AD62" s="8">
         <v>16.683949999999999</v>
       </c>
@@ -9969,7 +10045,7 @@
         <v>19647</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C69" s="4">
         <v>44</v>
@@ -10003,11 +10079,21 @@
       <c t="s" r="N69" s="4">
         <v>52</v>
       </c>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="6"/>
+      <c r="O69" s="5">
+        <v>0</v>
+      </c>
+      <c r="P69" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R69" s="7">
+        <v>0</v>
+      </c>
+      <c r="S69" s="6">
+        <v>-1</v>
+      </c>
       <c r="T69" s="6"/>
       <c r="U69" s="6"/>
       <c r="V69" s="6"/>
@@ -10021,7 +10107,9 @@
       <c r="AD69" s="8"/>
       <c r="AE69" s="6"/>
       <c r="AF69" s="9"/>
-      <c r="AG69" s="5"/>
+      <c r="AG69" s="5">
+        <v>0</v>
+      </c>
       <c r="AH69" s="10">
         <v>2</v>
       </c>
@@ -10802,7 +10890,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10836,25 +10924,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>10466.200000000001</v>
+      </c>
+      <c r="P76" s="5">
+        <v>10466.200000000001</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.12141544603725296</v>
+      </c>
+      <c r="R76" s="7">
+        <v>129</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.051470588235294157</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.32351531596950184</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.078906766543731244</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.041527536259578446</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.018832575337753912</v>
+      </c>
+      <c r="X76" s="8">
+        <v>50.43978548387097</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.37096774193548387</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.8230282442748091</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>23.786723728813559</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>28.144818000000001</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>35.817204838709678</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.30645161290322581</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-196.30000000000001</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -14118,7 +14242,9 @@
       <c r="AB102" s="8">
         <v>6.9260416666666664</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>13.776615</v>
+      </c>
       <c r="AD102" s="8">
         <v>18.919090909090908</v>
       </c>
@@ -21026,7 +21152,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21062,25 +21188,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>9472.3899999999994</v>
+      </c>
+      <c r="P158" s="5">
+        <v>9472.3899999999994</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.12219860180297737</v>
+      </c>
+      <c r="R158" s="7">
+        <v>89</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.160377358490566</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.28366666701856658</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.015916648279895571</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.017997675349093523</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.00029147870811907029</v>
+      </c>
+      <c r="X158" s="8">
+        <v>46.75333333333333</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.17333333333333334</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.64000000000000001</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>10.61666629213483</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>13.746</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>25.053554999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>31.972222666666671</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.093333333333333338</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 1.757.527,31</t>
-  </si>
-  <si>
-    <t>R$ 9.764,04
-R$ 9.968,54</t>
-  </si>
-  <si>
-    <t>12.5%
-14.7%</t>
-  </si>
-  <si>
-    <t>102.6</t>
-  </si>
-  <si>
-    <t>6.5%</t>
-  </si>
-  <si>
-    <t>44.6%</t>
-  </si>
-  <si>
-    <t>(1.6%)</t>
+172</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.779.773,28</t>
+  </si>
+  <si>
+    <t>R$ 9.778,97
+R$ 9.981,97</t>
+  </si>
+  <si>
+    <t>12.7%
+14.9%</t>
+  </si>
+  <si>
+    <t>102.8</t>
+  </si>
+  <si>
+    <t>6.8%</t>
+  </si>
+  <si>
+    <t>44.4%</t>
+  </si>
+  <si>
+    <t>(1.5%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -947,28 +947,28 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>31.5</t>
-  </si>
-  <si>
-    <t>53.9%</t>
-  </si>
-  <si>
-    <t>21.0%</t>
+    <t>31.6</t>
+  </si>
+  <si>
+    <t>54.3%</t>
+  </si>
+  <si>
+    <t>21.2%</t>
   </si>
   <si>
     <t>6.9</t>
   </si>
   <si>
-    <t>8.8</t>
+    <t>8.9</t>
   </si>
   <si>
     <t>16.2</t>
   </si>
   <si>
-    <t>22.7</t>
-  </si>
-  <si>
-    <t>55.8%</t>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>55.6%</t>
   </si>
   <si>
     <t>-R$ 39.957,06</t>
@@ -5924,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5960,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>10427.73</v>
+      </c>
+      <c r="P36" s="5">
+        <v>10427.73</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.52959149696435404</v>
+      </c>
+      <c r="R36" s="7">
+        <v>129</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.81690140845070425</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.34279512415453794</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.0032926629285568386</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.029493571467615675</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.0033373514657552509</v>
+      </c>
+      <c r="X36" s="8">
+        <v>46.653703703703705</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.51851851851851849</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>10.762132352941178</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>20.381775700934579</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>38.06898148148148</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.29629629629629628</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6674,7 +6708,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6710,25 +6744,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>11818.24</v>
+      </c>
+      <c r="P42" s="5">
+        <v>11818.24</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.15092959683223239</v>
+      </c>
+      <c r="R42" s="7">
+        <v>122</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.15094339622641506</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.31334878120600024</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.0020418522554965885</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.029508031652767251</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0061627619679410807</v>
+      </c>
+      <c r="X42" s="8">
+        <v>27.803256321839079</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.59090909090909094</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.045977011494252873</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.0912353448275862</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>8.1312264367816098</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>14.339463</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>21.254980459770113</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.68965517241379315</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -25937,7 +26007,9 @@
       <c r="AB195" s="8">
         <v>12.612120779220779</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>18.846736</v>
+      </c>
       <c r="AD195" s="8">
         <v>25.816666233766234</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
@@ -911,34 +911,37 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-172</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.779.773,28</t>
-  </si>
-  <si>
-    <t>R$ 9.778,97
-R$ 9.981,97</t>
-  </si>
-  <si>
-    <t>12.7%
-14.9%</t>
-  </si>
-  <si>
-    <t>102.8</t>
-  </si>
-  <si>
-    <t>6.8%</t>
-  </si>
-  <si>
-    <t>44.4%</t>
-  </si>
-  <si>
-    <t>(1.5%)</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+174</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.798.550,32</t>
+  </si>
+  <si>
+    <t>R$ 9.774,73
+R$ 9.975,14</t>
+  </si>
+  <si>
+    <t>12.4%
+14.6%</t>
+  </si>
+  <si>
+    <t>102.9</t>
+  </si>
+  <si>
+    <t>6.9%</t>
+  </si>
+  <si>
+    <t>44.3%</t>
+  </si>
+  <si>
+    <t>(1.6%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -947,28 +950,28 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>31.6</t>
+    <t>31.7</t>
   </si>
   <si>
     <t>54.3%</t>
   </si>
   <si>
-    <t>21.2%</t>
-  </si>
-  <si>
-    <t>6.9</t>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>7.2</t>
   </si>
   <si>
     <t>8.9</t>
   </si>
   <si>
-    <t>16.2</t>
-  </si>
-  <si>
-    <t>22.8</t>
-  </si>
-  <si>
-    <t>55.6%</t>
+    <t>16.5</t>
+  </si>
+  <si>
+    <t>23.0</t>
+  </si>
+  <si>
+    <t>55.3%</t>
   </si>
   <si>
     <t>-R$ 39.957,06</t>
@@ -2249,10 +2252,10 @@
         <v>0.016806722689075571</v>
       </c>
       <c r="T7" s="6">
-        <v>0.34484332259715289</v>
+        <v>0.34254573222899504</v>
       </c>
       <c r="U7" s="6">
-        <v>0.018267654809116442</v>
+        <v>0.015970064440958567</v>
       </c>
       <c r="V7" s="6">
         <v>0.027697634458921181</v>
@@ -5694,7 +5697,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5730,25 +5733,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>11391.1</v>
+      </c>
+      <c r="P34" s="5">
+        <v>11391.1</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-0.25170698124784041</v>
+      </c>
+      <c r="R34" s="7">
+        <v>151</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0.013422818791946289</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0.21317626041383186</v>
+      </c>
+      <c r="U34" s="6">
+        <v>-0.13385782760225087</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.054484685412295557</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.023807226694524671</v>
+      </c>
+      <c r="X34" s="8">
+        <v>47.241159130434781</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.42608695652173911</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.71304347826086956</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>33.23388543046358</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>0.7670030303030303</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>37.367434000000003</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>42.091739130434782</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.16521739130434782</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -6002,7 +6041,9 @@
       <c r="AB36" s="8">
         <v>20.381775700934579</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>31.345972</v>
+      </c>
       <c r="AD36" s="8">
         <v>38.06898148148148</v>
       </c>
@@ -15996,7 +16037,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>14.861777</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19103,7 +19146,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19139,25 +19182,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>7385.9399999999996</v>
+      </c>
+      <c r="P141" s="5">
+        <v>7385.9399999999996</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.38115879154168919</v>
+      </c>
+      <c r="R141" s="7">
+        <v>76</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.28813559322033888</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.36602723553129324</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.044210378096762225</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.064296758435622284</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.032660974770983793</v>
+      </c>
+      <c r="X141" s="8">
+        <v>29.930612244897958</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.91836734693877553</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0.24489795918367346</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>14.106798684210526</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>4.7698935483870972</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>18.939619</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>23.403402040816324</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.53061224489795922</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28319,112 +28398,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-174</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.798.550,32</t>
-  </si>
-  <si>
-    <t>R$ 9.774,73
-R$ 9.975,14</t>
-  </si>
-  <si>
-    <t>12.4%
-14.6%</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.808.735,26</t>
+  </si>
+  <si>
+    <t>R$ 9.776,95
+R$ 9.976,34</t>
+  </si>
+  <si>
+    <t>12.1%
+14.3%</t>
   </si>
   <si>
     <t>102.9</t>
   </si>
   <si>
-    <t>6.9%</t>
+    <t>6.6%</t>
   </si>
   <si>
     <t>44.3%</t>
   </si>
   <si>
-    <t>(1.6%)</t>
+    <t>(1.5%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -956,7 +956,7 @@
     <t>54.3%</t>
   </si>
   <si>
-    <t>21.6%</t>
+    <t>21.7%</t>
   </si>
   <si>
     <t>7.2</t>
@@ -971,10 +971,10 @@
     <t>23.0</t>
   </si>
   <si>
-    <t>55.3%</t>
-  </si>
-  <si>
-    <t>-R$ 39.957,06</t>
+    <t>55.2%</t>
+  </si>
+  <si>
+    <t>-R$ 40.026,86</t>
   </si>
   <si>
     <t>2.94</t>
@@ -4876,7 +4876,7 @@
         <v>-306.19999999999999</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -11091,7 +11091,7 @@
         <v>-196.30000000000001</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -12654,7 +12654,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12688,25 +12688,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>10184.940000000001</v>
+      </c>
+      <c r="P89" s="5">
+        <v>10184.940000000001</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.18965779249866133</v>
+      </c>
+      <c r="R89" s="7">
+        <v>86</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.28333333333333333</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.45338582259689308</v>
+      </c>
+      <c r="U89" s="6">
+        <v>0.12591997596451229</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.018925835596478723</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0058987583628376796</v>
+      </c>
+      <c r="X89" s="8">
+        <v>37.207264102564103</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.58974358974358976</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.4358974358974359</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>10.260185555555555</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>10.743694594594595</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>28.549146153846152</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.28205128205128205</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-69.799999999999997</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14236,7 +14270,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -16567,7 +16601,7 @@
         <v>-120.8</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -24736,7 +24770,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25707,7 +25741,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27018,7 +27052,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28403,7 +28437,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.808.735,26</t>
-  </si>
-  <si>
-    <t>R$ 9.776,95
-R$ 9.976,34</t>
-  </si>
-  <si>
-    <t>12.1%
-14.3%</t>
-  </si>
-  <si>
-    <t>102.9</t>
-  </si>
-  <si>
-    <t>6.6%</t>
-  </si>
-  <si>
-    <t>44.3%</t>
-  </si>
-  <si>
-    <t>(1.5%)</t>
+181</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.842.507,34</t>
+  </si>
+  <si>
+    <t>R$ 9.646,64
+R$ 9.832,22</t>
+  </si>
+  <si>
+    <t>12.0%
+14.1%</t>
+  </si>
+  <si>
+    <t>101.4</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>43.9%</t>
+  </si>
+  <si>
+    <t>(1.6%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -950,31 +950,31 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>31.7</t>
+    <t>31.6</t>
   </si>
   <si>
     <t>54.3%</t>
   </si>
   <si>
-    <t>21.7%</t>
+    <t>21.5%</t>
   </si>
   <si>
     <t>7.2</t>
   </si>
   <si>
-    <t>8.9</t>
-  </si>
-  <si>
-    <t>16.5</t>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>16.4</t>
   </si>
   <si>
     <t>23.0</t>
   </si>
   <si>
-    <t>55.2%</t>
-  </si>
-  <si>
-    <t>-R$ 40.026,86</t>
+    <t>55.5%</t>
+  </si>
+  <si>
+    <t>-R$ 40.483,06</t>
   </si>
   <si>
     <t>2.94</t>
@@ -7920,7 +7920,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7956,25 +7956,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1128.4200000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1128.4200000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.046636589445936849</v>
+      </c>
+      <c r="R51" s="7">
+        <v>13</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.071428571428571397</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.39128161500150649</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.045493699154570105</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.079601566792506323</v>
+      </c>
+      <c r="X51" s="8">
+        <v>107.34999999999999</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.9892857142857139</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>36.666649999999997</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>48.25</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8847,7 +8881,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>12.522024999999999</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -18732,7 +18768,7 @@
         <v>19787</v>
       </c>
       <c r="B137" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C137" s="4">
         <v>44</v>
@@ -18766,27 +18802,61 @@
       <c t="s" r="N137" s="4">
         <v>52</v>
       </c>
-      <c r="O137" s="5"/>
-      <c r="P137" s="5"/>
-      <c r="Q137" s="6"/>
-      <c r="R137" s="7"/>
-      <c r="S137" s="6"/>
-      <c r="T137" s="6"/>
-      <c r="U137" s="6"/>
-      <c r="V137" s="6"/>
-      <c r="W137" s="6"/>
-      <c r="X137" s="8"/>
-      <c r="Y137" s="6"/>
-      <c r="Z137" s="6"/>
-      <c r="AA137" s="8"/>
-      <c r="AB137" s="8"/>
+      <c r="O137" s="5">
+        <v>3429.5599999999999</v>
+      </c>
+      <c r="P137" s="5">
+        <v>3429.5599999999999</v>
+      </c>
+      <c r="Q137" s="6">
+        <v>0.3049579544157377</v>
+      </c>
+      <c r="R137" s="7">
+        <v>36</v>
+      </c>
+      <c r="S137" s="6">
+        <v>0</v>
+      </c>
+      <c r="T137" s="6">
+        <v>0.016738094682699822</v>
+      </c>
+      <c r="U137" s="6">
+        <v>-0.28478454962152577</v>
+      </c>
+      <c r="V137" s="6">
+        <v>0.011768856646333641</v>
+      </c>
+      <c r="W137" s="6">
+        <v>-0.024329068451929694</v>
+      </c>
+      <c r="X137" s="8">
+        <v>35.351113333333338</v>
+      </c>
+      <c r="Y137" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z137" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA137" s="8">
+        <v>7.3773138888888887</v>
+      </c>
+      <c r="AB137" s="8">
+        <v>12.879999999999999</v>
+      </c>
       <c r="AC137" s="8">
         <v>20.872222000000001</v>
       </c>
-      <c r="AD137" s="8"/>
-      <c r="AE137" s="6"/>
+      <c r="AD137" s="8">
+        <v>27.814446666666665</v>
+      </c>
+      <c r="AE137" s="6">
+        <v>0.46666666666666667</v>
+      </c>
       <c r="AF137" s="9"/>
-      <c r="AG137" s="5"/>
+      <c r="AG137" s="5">
+        <v>-236.5</v>
+      </c>
       <c r="AH137" s="10">
         <v>2</v>
       </c>
@@ -20490,7 +20560,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20526,25 +20596,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>8141.04</v>
+      </c>
+      <c r="P151" s="5">
+        <v>8141.04</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>0.15493437292521395</v>
+      </c>
+      <c r="R151" s="7">
+        <v>93</v>
+      </c>
+      <c r="S151" s="6">
+        <v>0.13414634146341453</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.31744876575965725</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.0060541282194903848</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.032262708450026038</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.010545581399919421</v>
+      </c>
+      <c r="X151" s="8">
+        <v>23.458958750000001</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>4.2614698924731185</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.4160341772151899</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>6.6220739999999996</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>13.526875</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.9375</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21240,7 +21346,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21276,25 +21382,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>8171.3299999999999</v>
+      </c>
+      <c r="P157" s="5">
+        <v>8171.3299999999999</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>0.26391393791279327</v>
+      </c>
+      <c r="R157" s="7">
+        <v>81</v>
+      </c>
+      <c r="S157" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.30164744294992368</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.0016375302429347488</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.025266388702940647</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.0076621553651608732</v>
+      </c>
+      <c r="X157" s="8">
+        <v>28.073148611111108</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>8.5993750000000002</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>4.1343920634920632</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>13.044824999999999</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>19.010648611111108</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.68055555555555558</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -22232,7 +22374,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22268,25 +22410,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>5280.7799999999997</v>
+      </c>
+      <c r="P165" s="5">
+        <v>5280.7799999999997</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.42827168673916161</v>
+      </c>
+      <c r="R165" s="7">
+        <v>54</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.47058823529411764</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.31474922265271421</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.014705895719950464</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.031013032165702795</v>
+      </c>
+      <c r="W165" s="6">
+        <v>0.0028865054026109781</v>
+      </c>
+      <c r="X165" s="8">
+        <v>18.851724137931036</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.93103448275862066</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>4.2629629629629626</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>1.0086206896551724</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>5.3541749999999997</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>12.217241379310344</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.96551724137931039</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-219.69999999999999</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
@@ -22327,7 +22505,7 @@
         <v>19879</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
@@ -22363,25 +22541,59 @@
       <c t="s" r="N166" s="4">
         <v>52</v>
       </c>
-      <c r="O166" s="5"/>
-      <c r="P166" s="5"/>
-      <c r="Q166" s="6"/>
-      <c r="R166" s="7"/>
-      <c r="S166" s="6"/>
-      <c r="T166" s="6"/>
-      <c r="U166" s="6"/>
-      <c r="V166" s="6"/>
-      <c r="W166" s="6"/>
-      <c r="X166" s="8"/>
-      <c r="Y166" s="6"/>
-      <c r="Z166" s="6"/>
-      <c r="AA166" s="8"/>
-      <c r="AB166" s="8"/>
+      <c r="O166" s="5">
+        <v>7620.9499999999998</v>
+      </c>
+      <c r="P166" s="5">
+        <v>7620.9499999999998</v>
+      </c>
+      <c r="Q166" s="6">
+        <v>0.33595407134718203</v>
+      </c>
+      <c r="R166" s="7">
+        <v>67</v>
+      </c>
+      <c r="S166" s="6">
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="T166" s="6">
+        <v>0.19527963049226146</v>
+      </c>
+      <c r="U166" s="6">
+        <v>-0.087569620585360095</v>
+      </c>
+      <c r="V166" s="6">
+        <v>0.012697432734764038</v>
+      </c>
+      <c r="W166" s="6">
+        <v>-0.0046074964407324549</v>
+      </c>
+      <c r="X166" s="8">
+        <v>40.511615151515151</v>
+      </c>
+      <c r="Y166" s="6">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="Z166" s="6">
+        <v>0.42424242424242425</v>
+      </c>
+      <c r="AA166" s="8">
+        <v>4.4007692307692308</v>
+      </c>
+      <c r="AB166" s="8">
+        <v>22.688021875</v>
+      </c>
       <c r="AC166" s="8"/>
-      <c r="AD166" s="8"/>
-      <c r="AE166" s="6"/>
+      <c r="AD166" s="8">
+        <v>33.349493939393938</v>
+      </c>
+      <c r="AE166" s="6">
+        <v>0.36363636363636365</v>
+      </c>
       <c r="AF166" s="9"/>
-      <c r="AG166" s="5"/>
+      <c r="AG166" s="5">
+        <v>0</v>
+      </c>
       <c r="AH166" s="10">
         <v>3</v>
       </c>
